--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487789_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487789_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4747</v>
+        <v>6.9459</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3498</v>
+        <v>3.9678</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1249</v>
+        <v>2.9781</v>
       </c>
       <c r="G2" t="n">
         <v>3.4233</v>
@@ -610,13 +610,13 @@
         <v>2.9137</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9057</v>
+        <v>1.3769</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9159</v>
+        <v>0.5339</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9898</v>
+        <v>0.843</v>
       </c>
       <c r="V2" t="n">
         <v>1.5213</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4346</v>
+        <v>5.3874</v>
       </c>
       <c r="E3" t="n">
-        <v>1.96</v>
+        <v>2.412</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4746</v>
+        <v>2.9754</v>
       </c>
       <c r="G3" t="n">
         <v>3.0435</v>
@@ -688,13 +688,13 @@
         <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6616</v>
+        <v>0.6143999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2486</v>
+        <v>0.2034</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9102</v>
+        <v>0.4111</v>
       </c>
       <c r="V3" t="n">
         <v>1.5213</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3496</v>
+        <v>2.6688</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6897</v>
+        <v>0.8621</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6599</v>
+        <v>1.8067</v>
       </c>
       <c r="G4" t="n">
         <v>3.7862</v>
@@ -766,13 +766,13 @@
         <v>1.4568</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2284</v>
+        <v>0.5475</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2701</v>
+        <v>0.4425</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0417</v>
+        <v>0.1051</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.353</v>
+        <v>1.1433</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0104</v>
+        <v>-1.4107</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6574</v>
+        <v>2.5539</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3588</v>
+        <v>-0.2359</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2069</v>
+        <v>-0.5609</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1519</v>
+        <v>0.3249</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3426</v>
+        <v>-0.9135</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2642</v>
+        <v>-1.414</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0784</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0162</v>
+        <v>0.6776</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0573</v>
+        <v>0.8531</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0735</v>
+        <v>-0.1755</v>
       </c>
       <c r="P5" t="n">
+        <v>1.4568</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.2081</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.6649</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.0776</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.2891</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.2114</v>
+      </c>
+      <c r="V5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>-1.0406</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.0406</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.3292</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.4784</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.8508</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-2.3351</v>
-      </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0756</v>
+        <v>1.1203</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1227</v>
+        <v>-1.8431</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1983</v>
+        <v>2.9634</v>
       </c>
       <c r="G6" t="n">
         <v>1.3471</v>
@@ -922,13 +922,13 @@
         <v>1.4568</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0228</v>
+        <v>0.0219</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4567</v>
+        <v>-0.1771</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4339</v>
+        <v>0.199</v>
       </c>
       <c r="V6" t="n">
         <v>0.5838</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4145</v>
+        <v>1.0157</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9045</v>
+        <v>-1.6848</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3191</v>
+        <v>2.7005</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2359</v>
+        <v>-0.227</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5609</v>
+        <v>-1.7251</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3249</v>
+        <v>1.4981</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9135</v>
+        <v>-0.6147</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.414</v>
+        <v>-1.8597</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5004999999999999</v>
+        <v>1.245</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6776</v>
+        <v>0.3877</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8531</v>
+        <v>0.1346</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1755</v>
+        <v>0.2531</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>2.4974</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8064</v>
+        <v>-0.236</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7829</v>
+        <v>-0.0514</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0235</v>
+        <v>-0.1846</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>G. CLARKE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0616</v>
+        <v>0.7825</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3511</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2895</v>
+        <v>-0.0547</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.227</v>
+        <v>0.9339</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7251</v>
+        <v>1.0302</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4981</v>
+        <v>-0.0963</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6147</v>
+        <v>2.3221</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.8597</v>
+        <v>1.9572</v>
       </c>
       <c r="L8" t="n">
-        <v>1.245</v>
+        <v>0.3649</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3877</v>
+        <v>-1.3883</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1346</v>
+        <v>-0.927</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2531</v>
+        <v>-0.4613</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2487</v>
+        <v>-2.0812</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4974</v>
+        <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3133</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7177</v>
+        <v>0.3663</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5956</v>
+        <v>0.5011</v>
       </c>
       <c r="V8" t="n">
         <v>0.23</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. CLARKE</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1202</v>
+        <v>-0.5583</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4924</v>
+        <v>0.5102</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6125</v>
+        <v>-1.0685</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9339</v>
+        <v>0.3588</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0302</v>
+        <v>0.2069</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0963</v>
+        <v>0.1519</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3221</v>
+        <v>0.3426</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9572</v>
+        <v>0.2642</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3649</v>
+        <v>0.0784</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3883</v>
+        <v>0.0162</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.927</v>
+        <v>-0.0573</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4613</v>
+        <v>0.0735</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0353</v>
+        <v>1.418</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0215</v>
+        <v>0.9782</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0567</v>
+        <v>0.4398</v>
       </c>
       <c r="V9" t="n">
-        <v>0.23</v>
+        <v>-2.3351</v>
       </c>
       <c r="W9" t="n">
         <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.483</v>
+        <v>-3.8895</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.1479</v>
+        <v>-5.2021</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6649</v>
+        <v>1.3126</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6821</v>
@@ -1234,13 +1234,13 @@
         <v>1.2487</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4052</v>
+        <v>0.9987</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6277</v>
+        <v>0.3182</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0328</v>
+        <v>0.6805</v>
       </c>
       <c r="V10" t="n">
         <v>0.7076</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5558</v>
+        <v>-4.4299</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.1794</v>
+        <v>-6.3471</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6236</v>
+        <v>1.9172</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6858</v>
@@ -1312,13 +1312,13 @@
         <v>2.2893</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4411</v>
+        <v>1.5671</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9935</v>
+        <v>0.8259</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4476</v>
+        <v>0.7412</v>
       </c>
       <c r="V11" t="n">
         <v>-0.23</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.881399999999998</v>
+        <v>10.1862</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.203300000000002</v>
+        <v>-7.8985</v>
       </c>
       <c r="F12" t="n">
-        <v>18.0849</v>
+        <v>18.0846</v>
       </c>
       <c r="G12" t="n">
-        <v>6.061999999999998</v>
+        <v>6.061999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>1.4287</v>
@@ -1369,13 +1369,13 @@
         <v>1.3081</v>
       </c>
       <c r="L12" t="n">
-        <v>5.674099999999998</v>
+        <v>5.674099999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9202000000000004</v>
+        <v>-0.9202000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1206000000000001</v>
+        <v>0.1206</v>
       </c>
       <c r="O12" t="n">
         <v>-1.0409</v>
@@ -1390,10 +1390,10 @@
         <v>16.6494</v>
       </c>
       <c r="S12" t="n">
-        <v>5.7934</v>
+        <v>7.0983</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8458</v>
+        <v>3.1508</v>
       </c>
       <c r="U12" t="n">
         <v>3.9476</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2736</v>
+        <v>5.2952</v>
       </c>
       <c r="E13" t="n">
         <v>2.6049</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6687</v>
+        <v>2.6903</v>
       </c>
       <c r="G13" t="n">
         <v>1.6979</v>
@@ -1468,13 +1468,13 @@
         <v>2.4974</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4867</v>
+        <v>-0.4652</v>
       </c>
       <c r="T13" t="n">
         <v>-0.7086</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2219</v>
+        <v>0.2434</v>
       </c>
       <c r="V13" t="n">
         <v>1.9813</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1833</v>
+        <v>3.4509</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6209</v>
+        <v>1.1567</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5623</v>
+        <v>2.2942</v>
       </c>
       <c r="G14" t="n">
         <v>1.5157</v>
@@ -1546,13 +1546,13 @@
         <v>2.9137</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8298</v>
+        <v>-0.5622</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2925</v>
+        <v>-0.7567</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4626</v>
+        <v>0.1945</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. MORENO MARTIN</t>
+          <t>T. TEIXEIRA DO VALE DIAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9423</v>
+        <v>1.1023</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.8816</v>
+        <v>0.2887</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8239</v>
+        <v>0.8137</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.8091</v>
+        <v>1.9046</v>
       </c>
       <c r="H15" t="n">
-        <v>0.885</v>
+        <v>0.3371</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.6941</v>
+        <v>1.5675</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3709</v>
+        <v>2.0517</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1425</v>
+        <v>-0.369</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7715</v>
+        <v>2.4207</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.18</v>
+        <v>-0.1471</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2575</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9225</v>
+        <v>-0.8532</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.5786</v>
+        <v>-1.2487</v>
       </c>
       <c r="R15" t="n">
-        <v>3.9542</v>
+        <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6057</v>
+        <v>-0.5723</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0961</v>
+        <v>-0.5143</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5096000000000001</v>
+        <v>-0.058</v>
       </c>
       <c r="V15" t="n">
         <v>-0.23</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4599</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. TEIXEIRA DO VALE DIAS</t>
+          <t>J. JOHNSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4325</v>
+        <v>0.6707</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0328</v>
+        <v>-1.2742</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4653</v>
+        <v>1.9449</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9046</v>
+        <v>-2.4722</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3371</v>
+        <v>-0.7504</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5675</v>
+        <v>-1.7218</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0517</v>
+        <v>-1.4474</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.369</v>
+        <v>0.0296</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4207</v>
+        <v>-1.4769</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1471</v>
+        <v>-1.0249</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7060999999999999</v>
+        <v>-0.78</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8532</v>
+        <v>-0.2449</v>
       </c>
       <c r="P16" t="n">
+        <v>3.1218</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.2081</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.3299</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-1.1463</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.7862</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.3601</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.1675</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.1675</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-1.2487</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.2487</v>
-      </c>
-      <c r="S16" t="n">
-        <v>-1.2422</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-0.8358</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.4064</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. JOHNSON</t>
+          <t>V. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3959</v>
+        <v>-1.3428</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7028</v>
+        <v>-3.8105</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3069</v>
+        <v>2.4677</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4722</v>
+        <v>-0.8091</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7504</v>
+        <v>0.885</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7218</v>
+        <v>-1.6941</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4474</v>
+        <v>0.3709</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0296</v>
+        <v>1.1425</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4769</v>
+        <v>-0.7715</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0249</v>
+        <v>-1.18</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.78</v>
+        <v>-0.2575</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2449</v>
+        <v>-0.9225</v>
       </c>
       <c r="P17" t="n">
-        <v>3.1218</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2081</v>
+        <v>-4.5786</v>
       </c>
       <c r="R17" t="n">
-        <v>3.3299</v>
+        <v>3.9542</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.213</v>
+        <v>0.3206</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.2148</v>
+        <v>0.1672</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9981</v>
+        <v>0.1534</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1675</v>
+        <v>-0.23</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.1596</v>
+        <v>-2.8993</v>
       </c>
       <c r="E18" t="n">
         <v>-2.0073</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1523</v>
+        <v>-0.892</v>
       </c>
       <c r="G18" t="n">
         <v>1.3928</v>
@@ -1858,13 +1858,13 @@
         <v>0.6244</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5337</v>
+        <v>-0.2734</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3138</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2198</v>
+        <v>0.0405</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5213</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3119</v>
+        <v>-3.3437</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9299</v>
+        <v>-3.2514</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.382</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-3.7119</v>
@@ -1936,13 +1936,13 @@
         <v>1.6649</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2036</v>
+        <v>-0.2354</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2172</v>
+        <v>-0.1043</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4208</v>
+        <v>-0.1311</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0614</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.8294</v>
+        <v>-4.6151</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9248</v>
+        <v>-3.7105</v>
       </c>
       <c r="F20" t="n">
         <v>-0.9046</v>
@@ -2014,10 +2014,10 @@
         <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5467</v>
+        <v>-0.3324</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3667</v>
+        <v>-0.1524</v>
       </c>
       <c r="U20" t="n">
         <v>-0.18</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.0161</v>
+        <v>-5.7708</v>
       </c>
       <c r="E21" t="n">
-        <v>-8.831300000000001</v>
+        <v>-8.081200000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8152</v>
+        <v>2.3104</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1107</v>
@@ -2092,13 +2092,13 @@
         <v>3.9542</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.3435</v>
+        <v>-1.0982</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5287</v>
+        <v>-0.7786</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8148</v>
+        <v>-0.3196</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9376</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.881199999999998</v>
+        <v>-7.452600000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-18.0847</v>
+        <v>-18.0848</v>
       </c>
       <c r="F22" t="n">
-        <v>9.203399999999998</v>
+        <v>10.6323</v>
       </c>
       <c r="G22" t="n">
         <v>-6.0619</v>
@@ -2143,10 +2143,10 @@
         <v>-4.6331</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9201999999999995</v>
+        <v>0.9201999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1206999999999998</v>
+        <v>-0.1206999999999994</v>
       </c>
       <c r="L22" t="n">
         <v>1.0409</v>
@@ -2158,10 +2158,10 @@
         <v>-1.3082</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.674199999999999</v>
+        <v>-5.6742</v>
       </c>
       <c r="P22" t="n">
-        <v>5.2029</v>
+        <v>5.202900000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>-16.6494</v>
@@ -2170,13 +2170,13 @@
         <v>21.8523</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.7935</v>
+        <v>-4.364800000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.9476</v>
+        <v>-3.9477</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.8458</v>
+        <v>-0.4169999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-2.229</v>
